--- a/pipelines/Demo_data/Output_data/out_ПК.xlsx
+++ b/pipelines/Demo_data/Output_data/out_ПК.xlsx
@@ -494,10 +494,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,10 +536,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18272.24</t>
-        </is>
+      <c r="F3" t="n">
+        <v>18272.24</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -582,10 +578,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,10 +620,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -670,10 +662,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -714,10 +704,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -758,10 +746,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -802,10 +788,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -846,10 +830,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -886,10 +868,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -930,10 +910,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -974,10 +952,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1018,10 +994,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1062,10 +1036,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,10 +1078,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1150,10 +1120,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1194,10 +1162,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1238,10 +1204,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1282,10 +1246,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1326,10 +1288,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1370,10 +1330,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1414,10 +1372,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1458,10 +1414,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1502,10 +1456,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1546,10 +1498,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1590,10 +1540,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1634,10 +1582,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1678,10 +1624,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F29" t="n">
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1722,10 +1666,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1766,10 +1708,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1810,10 +1750,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F32" t="n">
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1854,10 +1792,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1898,10 +1834,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1942,10 +1876,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1986,10 +1918,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F36" t="n">
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2030,10 +1960,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F37" t="n">
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2074,10 +2002,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2118,10 +2044,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F39" t="n">
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2162,10 +2086,8 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F40" t="n">
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2206,10 +2128,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F41" t="n">
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2250,10 +2170,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F42" t="n">
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2294,10 +2212,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2338,10 +2254,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2382,10 +2296,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F45" t="n">
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2426,10 +2338,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F46" t="n">
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2470,10 +2380,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F47" t="n">
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2514,10 +2422,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F48" t="n">
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2558,10 +2464,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F49" t="n">
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2602,10 +2506,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F50" t="n">
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2646,10 +2548,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2690,10 +2590,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F52" t="n">
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2734,10 +2632,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F53" t="n">
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2778,10 +2674,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2822,10 +2716,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F55" t="n">
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2866,10 +2758,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F56" t="n">
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2910,10 +2800,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2954,10 +2842,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2998,10 +2884,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F59" t="n">
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3042,10 +2926,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F60" t="n">
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3086,10 +2968,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F61" t="n">
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3130,10 +3010,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3174,10 +3052,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F63" t="n">
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3218,10 +3094,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F64" t="n">
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3262,10 +3136,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F65" t="n">
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3306,10 +3178,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F66" t="n">
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3350,10 +3220,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F67" t="n">
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3394,10 +3262,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F68" t="n">
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3446,10 +3312,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F69" t="n">
+        <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3498,10 +3362,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F70" t="n">
+        <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3550,10 +3412,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F71" t="n">
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3602,10 +3462,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F72" t="n">
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3654,10 +3512,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F73" t="n">
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3706,10 +3562,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F74" t="n">
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3758,10 +3612,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F75" t="n">
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3810,10 +3662,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F76" t="n">
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3862,10 +3712,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F77" t="n">
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3914,10 +3762,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F78" t="n">
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3966,10 +3812,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F79" t="n">
+        <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4018,10 +3862,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F80" t="n">
+        <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4070,10 +3912,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F81" t="n">
+        <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4122,10 +3962,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F82" t="n">
+        <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4174,10 +4012,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F83" t="n">
+        <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4226,10 +4062,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F84" t="n">
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4278,10 +4112,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F85" t="n">
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4330,10 +4162,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F86" t="n">
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4382,10 +4212,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F87" t="n">
+        <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4434,10 +4262,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F88" t="n">
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4486,10 +4312,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F89" t="n">
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4538,10 +4362,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F90" t="n">
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4590,10 +4412,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F91" t="n">
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4642,10 +4462,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F92" t="n">
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4694,10 +4512,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F93" t="n">
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/out_ПК.xlsx
+++ b/pipelines/Demo_data/Output_data/out_ПК.xlsx
@@ -494,8 +494,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -536,8 +538,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>18272.24</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18272.24</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -578,8 +582,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -620,8 +626,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -662,8 +670,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -704,8 +714,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,8 +758,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -788,8 +802,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -830,8 +846,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -868,8 +886,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -910,8 +930,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -952,8 +974,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -994,8 +1018,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1036,8 +1062,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1078,8 +1106,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1120,8 +1150,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1162,8 +1194,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1204,8 +1238,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1246,8 +1282,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1288,8 +1326,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1330,8 +1370,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1372,8 +1414,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1414,8 +1458,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1456,8 +1502,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1498,8 +1546,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1540,8 +1590,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1582,8 +1634,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1624,8 +1678,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1666,8 +1722,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1708,8 +1766,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1750,8 +1810,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1792,8 +1854,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1834,8 +1898,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1876,8 +1942,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1918,8 +1986,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1960,8 +2030,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2002,8 +2074,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2044,8 +2118,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2086,8 +2162,10 @@
           <t>001*********</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2128,8 +2206,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2170,8 +2250,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2212,8 +2294,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2254,8 +2338,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2296,8 +2382,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2338,8 +2426,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2380,8 +2470,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2422,8 +2514,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2464,8 +2558,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2506,8 +2602,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2548,8 +2646,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2590,8 +2690,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2632,8 +2734,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2674,8 +2778,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2716,8 +2822,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2758,8 +2866,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2800,8 +2910,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2842,8 +2954,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2884,8 +2998,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2926,8 +3042,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2968,8 +3086,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3010,8 +3130,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3052,8 +3174,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3094,8 +3218,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3136,8 +3262,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3178,8 +3306,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3220,8 +3350,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3262,8 +3394,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3312,8 +3446,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>0</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3362,8 +3498,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>0</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3412,8 +3550,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3462,8 +3602,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>0</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3512,8 +3654,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3562,8 +3706,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3612,8 +3758,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>0</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,8 +3810,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3712,8 +3862,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3762,8 +3914,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3812,8 +3966,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3862,8 +4018,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>0</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3912,8 +4070,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3962,8 +4122,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4012,8 +4174,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4062,8 +4226,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>0</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4112,8 +4278,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>0</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4162,8 +4330,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4212,8 +4382,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4262,8 +4434,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4312,8 +4486,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4362,8 +4538,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4412,8 +4590,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4462,8 +4642,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4512,8 +4694,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
